--- a/GRC_WB_timeseries.xlsx
+++ b/GRC_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -437,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -507,8 +510,11 @@
       <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -525,46 +531,49 @@
         <v>10706000</v>
       </c>
       <c r="G2">
+        <v>96529587274.2906</v>
+      </c>
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>9466.66238502174</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>17.7296381357108</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>42.8867730557478</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>24.2015020301837</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>24.3139691998969</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>20.433499109463</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>20.8690484353929</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>-19.9251437211894</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>15.3345693084335</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>4721071253.78782</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>2.62427529393431</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>39.0357306279462</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -581,34 +590,37 @@
         <v>-25741000</v>
       </c>
       <c r="G3">
+        <v>103680863712.844</v>
+      </c>
+      <c r="H3">
         <v>3.09999970633838</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>10046.6663875475</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>16.72267030785</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>23.3964817257264</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>19.4558456445745</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>6400005237.09394</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>3.44224332091619</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>37.5415185885243</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>7.572</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -625,34 +637,37 @@
         <v>46498000</v>
       </c>
       <c r="G4">
+        <v>114608178405.434</v>
+      </c>
+      <c r="H4">
         <v>0.700000337119789</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>11021.012224607</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>16.1733636771943</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>22.9654502840077</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>15.8770737923919</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>5937644102.6132</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>2.9758897895568</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>37.7870755959724</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>8.927</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -669,34 +684,37 @@
         <v>-22432000</v>
       </c>
       <c r="G5">
+        <v>107295704518.43</v>
+      </c>
+      <c r="H5">
         <v>-1.60000002186294</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>10257.3085789073</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>16.8331847640658</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>22.0392804676088</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>14.4112644439348</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>9135322990.04867</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>5.0990220884964</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>36.0330301689118</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>10.177</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -713,34 +731,37 @@
         <v>15786000</v>
       </c>
       <c r="G6">
+        <v>114980063202.247</v>
+      </c>
+      <c r="H6">
         <v>1.99999984724822</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>10937.0223808611</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>16.2103603574166</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>20.8301695683564</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>10.8740756809131</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>15809339689.2247</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>8.345595472052469</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>35.2202302292147</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>9.808</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -757,49 +778,52 @@
         <v>41595000</v>
       </c>
       <c r="G7">
+        <v>134974613913.811</v>
+      </c>
+      <c r="H7">
         <v>2.09971953235275</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>12779.081491606</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>37</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>18.0436516636729</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>44.5116468219634</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>35.4672219144454</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>21.7558214495402</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>8.93451415961518</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>-9.910728257093551</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>18.8429151205785</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>16118557930.3879</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>6.9810046257139</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>36.1256353436075</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>10.116</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -819,49 +843,52 @@
         <v>-25368000</v>
       </c>
       <c r="G8">
+        <v>142502984144.96</v>
+      </c>
+      <c r="H8">
         <v>1.38247057325857</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>13432.5262183244</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>18.0228219972902</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>44.399141747722</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>36.9516014585854</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>22.5075465825416</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>8.194552176327271</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>-8.39922010732962</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>0.553863883018494</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>19.075319278645</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>18782300412.3394</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>7.78003468926726</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>36.8209292630895</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>10.402</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -878,49 +905,52 @@
         <v>155663000</v>
       </c>
       <c r="G9">
+        <v>138766067640.085</v>
+      </c>
+      <c r="H9">
         <v>3.60288326516122</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>13015.9175046854</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>18.2422853905251</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>43.751756513997</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>38.7559496642107</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>23.0682195187208</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>5.53600266773481</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>19.9839667824621</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>-6.24408406085801</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>20.1397117181124</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>13652307050.7874</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>5.7602645690886</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>39.4385486529083</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>10.472</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -937,49 +967,52 @@
         <v>-275600000</v>
       </c>
       <c r="G10">
+        <v>139612812175.718</v>
+      </c>
+      <c r="H10">
         <v>3.43693579661333</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>13022.9648774809</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>18.1010217911552</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>44.1800994121609</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>40.1449572383943</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>26.0039798757566</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>4.76622572397641</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>18.2873485868102</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>-6.38305645948466</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>0.771396815776825</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>21.2361125370926</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>18501070728.0752</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>42.4898959577488</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>12.227</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -996,49 +1029,52 @@
         <v>57778039.8257633</v>
       </c>
       <c r="G11">
+        <v>137131371955.307</v>
+      </c>
+      <c r="H11">
         <v>2.65878562321184</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>12742.5404388143</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>18.6956372889632</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>43.4560111642327</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>40.5423118071002</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>28.7601191111593</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>2.63663306021981</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>18.3192044926137</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>-6.13594463178484</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>22.2860306923914</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>19352094677.8738</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>5.96424506943985</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>48.1760370261319</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>12.138</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1058,55 +1094,58 @@
         <v>1008469359.90368</v>
       </c>
       <c r="G12">
+        <v>125760166224.805</v>
+      </c>
+      <c r="H12">
         <v>4.13782699405849</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>11638.2010697215</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>34.4</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>18.942080044244</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>44.4473263233025</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>42.5018377669505</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>35.1013997962753</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>3.1511816249383</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>15.8840052875083</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>-4.20090394199092</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>0.808356404304504</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>23.309875911687</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>14594006578.5544</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>3.85891245914069</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>59.1126577488086</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>11.345</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1123,49 +1162,52 @@
         <v>-972406714.945479</v>
       </c>
       <c r="G13">
+        <v>132050474720.03</v>
+      </c>
+      <c r="H13">
         <v>4.65041459442163</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>12156.9572824221</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>19.3185597563907</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>43.8026037175959</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>40.4357813080368</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>33.6978743793252</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>3.37396832213867</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>14.8415967297389</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>-5.8010540026106</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>21.6130465155138</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>6244166654.25856</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>1.66789173892202</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>56.8576339551067</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>10.764</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1185,55 +1227,58 @@
         <v>649629399.473881</v>
       </c>
       <c r="G14">
+        <v>150253800085.865</v>
+      </c>
+      <c r="H14">
         <v>4.68313727063017</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>13782.195640943</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>35.5</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>19.7788964081303</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>43.2026585802198</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>39.5456935545875</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>29.6702347678407</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>3.62935871878873</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>13.5804806991988</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>-6.17801164285532</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>0.872591853141785</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>21.8769704329815</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>9431530975.46332</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>2.53504698999448</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>50.0533371904633</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>10.346</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:23">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1253,55 +1298,58 @@
         <v>451509689.580649</v>
       </c>
       <c r="G15">
+        <v>196930509813.384</v>
+      </c>
+      <c r="H15">
         <v>5.79682274294369</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>18020.612039764</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>32.8</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>19.4825367880777</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>43.1830691765025</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>38.4678548260115</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>29.0208197707737</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>3.53065027765552</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>12.0218143123171</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>-8.100128245903671</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>0.477636367082596</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>20.2520438018772</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>5801377074.94914</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>1.22406996338363</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>47.8943121550822</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>9.839</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:23">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1321,55 +1369,58 @@
         <v>1071329338.17154</v>
       </c>
       <c r="G16">
+        <v>234979615898.225</v>
+      </c>
+      <c r="H16">
         <v>5.37786634595851</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>21449.2552764245</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>33.6</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>19.6428208434707</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>44.5593874599535</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>36.7877644448115</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>29.2160067589458</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>2.89884810758171</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>11.2586872586873</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>-8.915053688305029</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>0.489336252212524</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>19.6220114639512</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>2707782609.03229</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>0.46196039556585</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>49.825317672568</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>10.628</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:23">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1389,55 +1440,58 @@
         <v>1507422828.30937</v>
       </c>
       <c r="G17">
+        <v>242315668619.405</v>
+      </c>
+      <c r="H17">
         <v>1.18350635493289</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>22054.1315756886</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>34.6</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>20.4795823716794</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>43.928487332671</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>37.0743679804993</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>29.3630031508258</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>3.54507273335077</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>11.2352590549433</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>-6.36585961405065</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>0.50652414560318</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>20.7928823703071</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>2287009892.67273</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>0.353275593210376</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>50.3555334391407</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>10.074</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:23">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1457,55 +1511,58 @@
         <v>4234934038.24931</v>
       </c>
       <c r="G18">
+        <v>269073415333.676</v>
+      </c>
+      <c r="H18">
         <v>6.44339762487436</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>24416.0232970275</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>35.1</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>20.4905653377788</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>43.1248180840893</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>36.0771842596001</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>30.329773779727</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>3.19594684144545</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>10.7513850415512</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>-6.01263072426302</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>0.630432784557343</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>20.3113525444312</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>2849953559.42375</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>0.361966375722178</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>51.1047465834807</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>8.906000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1525,55 +1582,58 @@
         <v>5260558422.64125</v>
       </c>
       <c r="G19">
+        <v>314226996944.108</v>
+      </c>
+      <c r="H19">
         <v>3.50686976639459</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>28440.7625328955</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>34</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>20.8256340521222</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>44.7050606293494</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>37.2352449846351</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>32.7774943504585</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>2.89500321516578</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>10.5442873728061</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>-6.79510292197407</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>0.523507833480835</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>20.5440647006846</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>3647605325.12089</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>0.364544288639561</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>54.5256818189044</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>8.351000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:23">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1593,55 +1653,58 @@
         <v>3208047654.48818</v>
       </c>
       <c r="G20">
+        <v>351121399546.485</v>
+      </c>
+      <c r="H20">
         <v>0.0574740238200775</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>31695.8331092209</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>33.6</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>21.0036498022038</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>47.8546535471323</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>37.5541284926224</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>34.3204916281311</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>4.15279708110293</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>10.5395374892775</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>-10.2661774047815</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>0.267854154109955</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>20.4892108105139</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>3489670238.03477</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>0.291765014595587</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>57.1052836264926</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>7.664</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:23">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1661,55 +1724,58 @@
         <v>2441572099.18153</v>
       </c>
       <c r="G21">
+        <v>326829054686.306</v>
+      </c>
+      <c r="H21">
         <v>-4.11927606715011</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>29425.4573200263</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>33.6</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>23.6284806116531</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>51.9680969068081</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>36.5112016848157</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>27.6480773891011</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>1.21007269197809</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>10.1516756588078</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>-15.4065372983558</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>-0.208124294877052</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>20.0467212280259</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>5486122597.5994</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>0.638122957216378</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>46.3779593986083</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>9.545999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:23">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1729,55 +1795,58 @@
         <v>1696659551.61851</v>
       </c>
       <c r="G22">
+        <v>296417644404.034</v>
+      </c>
+      <c r="H22">
         <v>-5.6937412158003</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>26653.0488008626</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>34.1</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>22.4102559565882</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>51.078647377558</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>37.9537602345474</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>29.1936843254168</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>4.71298907760393</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>12.008020524136</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>-11.1248021125621</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>-0.12720687687397</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>20.4346791237019</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>6352405963.38906</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>0.792574625878538</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>50.9225173052303</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>12.719</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:23">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1797,55 +1866,58 @@
         <v>1818561692.26179</v>
       </c>
       <c r="G23">
+        <v>283228079776.041</v>
+      </c>
+      <c r="H23">
         <v>-9.87677875300243</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>25504.7866510124</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>34.8</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>22.0783071279586</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>54.7841287756502</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>40.7396508078936</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>30.9853934922685</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>3.32985323350645</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>13.9344409358404</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>-10.7389119947317</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>-0.0986951887607574</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>22.4592713947757</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>6743416891.38218</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>0.792222436462402</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>56.2929962856516</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>17.973</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:23">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1865,55 +1937,58 @@
         <v>678300574.816381</v>
       </c>
       <c r="G24">
+        <v>238841140018.233</v>
+      </c>
+      <c r="H24">
         <v>-8.33113421099992</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>21624.346052551</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>36.3</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>22.557839474738</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>57.3762666302254</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>44.3396291981173</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>33.4284650145065</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>1.50152696177755</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>9.434475258292551</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>-9.644475862193771</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>-0.217248693108559</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>24.9543887136577</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>7255024354.91008</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>1.13518534780232</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>62.3942789758861</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>24.731</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:23">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -1933,55 +2008,58 @@
         <v>-697506784.3645999</v>
       </c>
       <c r="G25">
+        <v>236556279640.705</v>
+      </c>
+      <c r="H25">
         <v>-2.27211699888024</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>21573.3449762805</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>36.1</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>20.9297924686921</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>61.3545612333663</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>43.7607628112252</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>32.627537198852</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>-0.921269454256931</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>6.90421939769951</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>-14.0252952861954</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>-0.171341717243195</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>24.7308046940324</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>5763071364.05671</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>0.7786970413865359</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>62.9547463104465</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>27.686</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:23">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2001,55 +2079,58 @@
         <v>3016269457.47392</v>
       </c>
       <c r="G26">
+        <v>233911581521.062</v>
+      </c>
+      <c r="H26">
         <v>0.792225060962835</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>21474.7257123892</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>35.8</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>20.7227080595732</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>49.7478747922233</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>43.194299954025</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>33.9185692513027</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>-1.3122609640551</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>8.335236094620511</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>-4.07390521833749</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>-0.140445962548256</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>25.3987231791514</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>6236284818.73247</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>0.817946595802777</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>66.4335682565667</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>26.708</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:23">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2069,55 +2150,58 @@
         <v>1582602882.35692</v>
       </c>
       <c r="G27">
+        <v>194567373678.099</v>
+      </c>
+      <c r="H27">
         <v>-0.228301892172851</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>17980.7298238137</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>36</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>20.7679837462522</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>52.2111640982534</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>43.8507857974366</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>33.085423586627</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>-1.73588804765284</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>7.14511954040564</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>-6.18545961591712</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>-0.235559731721878</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>25.3959107582621</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>6027606781.10376</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>1.00382336570052</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>65.27180113912139</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>24.981</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:23">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2137,55 +2221,58 @@
         <v>-1763343599.34987</v>
       </c>
       <c r="G28">
+        <v>193097239005.87</v>
+      </c>
+      <c r="H28">
         <v>-0.0317947678412054</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>17919.2426377048</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>35</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>20.6180603140124</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>48.8551944521521</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>46.3937185703594</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>32.4782765724963</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>-0.825653978390973</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>6.933248853063</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>-0.106048681446585</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>-0.129703640937805</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>27.0349616993722</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>6851247713.21209</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>1.17793527461763</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>63.6576625890375</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>23.514</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:23">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2205,55 +2292,58 @@
         <v>155667865.391135</v>
       </c>
       <c r="G29">
+        <v>200381103984.298</v>
+      </c>
+      <c r="H29">
         <v>1.47312472702352</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>18631.9930129293</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>34.4</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>20.4384126534599</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>47.670388743995</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>45.683676231325</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>36.1032862068475</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>1.1212545203142</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>6.91722743238289</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>0.358555379698674</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>-0.08124404400587081</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>26.7428191688464</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>7803722132.38225</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>1.17146506354673</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>70.8826066741577</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>21.413</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:23">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2273,55 +2363,58 @@
         <v>519563248.700829</v>
       </c>
       <c r="G30">
+        <v>213298873494.394</v>
+      </c>
+      <c r="H30">
         <v>2.06467207892409</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>19873.4015238771</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>32.9</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>19.6597104516787</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>48.0218614049715</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>45.6693521629155</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>40.6071874522328</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>0.625621413453609</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>7.31999769412579</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>0.533730032794056</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>0.153979063034058</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>27.1083919768284</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>7578500698.89502</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>0.957333984886142</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>79.2381636063709</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>19.179</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:23">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2341,55 +2434,58 @@
         <v>626776340.982972</v>
       </c>
       <c r="G31">
+        <v>207305649887.019</v>
+      </c>
+      <c r="H31">
         <v>2.27718065334808</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>19335.3602002969</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>33.1</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>19.9791204523634</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>46.9259260449285</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>44.0152636432372</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>41.0298090980773</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>0.253007522038191</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>6.62155630739488</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>0.788416902869981</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>0.162428334355354</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>25.9324359654947</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>8507452886.82209</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>1.11072209501885</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>80.59010089117299</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>17.045</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:23">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2409,55 +2505,58 @@
         <v>648302177.3971781</v>
       </c>
       <c r="G32">
+        <v>191362985554.861</v>
+      </c>
+      <c r="H32">
         <v>-9.19623149726978</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>17886.733165236</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>33.6</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>22.7274940590434</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>58.0698817576878</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>44.0015590829144</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>38.8433569445986</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>-1.24798355581408</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>5.34587316270943</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>-9.595348125568799</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>0.115181528031826</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>24.9917156858479</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>11931180004.6485</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>1.80594966237986</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>70.29378644863949</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>15.899</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:23">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2477,55 +2576,58 @@
         <v>1227924446.9239</v>
       </c>
       <c r="G33">
+        <v>218303801895.326</v>
+      </c>
+      <c r="H33">
         <v>8.65449786002131</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>20654.7001960815</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>32.9</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>21.4974385558012</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>54.8325762184431</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>43.9497127949658</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>47.7522509396405</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1.22382501019854</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>4.89689448358315</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>-6.83951151779645</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>0.10138326883316</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>25.5777359596935</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>14447242598.1807</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>1.5615357940513</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>88.0126627401059</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>14.656</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:23">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2545,55 +2647,58 @@
         <v>2465620567.32035</v>
       </c>
       <c r="G34">
+        <v>218880566444.349</v>
+      </c>
+      <c r="H34">
         <v>5.74364902526337</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>20971.8349258283</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>33.4</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>19.9856875626536</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>50.5946031348852</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>45.0580295027497</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>58.6593231211582</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>9.64525981280638</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>5.16911841617299</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>-2.28718031344907</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>0.106463775038719</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>27.6693971786038</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>12061425398.4158</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>1.05795032274949</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>107.679207902405</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>12.426</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:23">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2613,55 +2718,58 @@
         <v>4050698303.42558</v>
       </c>
       <c r="G35">
+        <v>243498333237.802</v>
+      </c>
+      <c r="H35">
         <v>2.33212444945818</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>23400.7278817691</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>33.4</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>19.2868439733478</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>47.1947012803121</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>43.2372754204675</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>48.4480311941784</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>3.46480128513402</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>7.26940845494491</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>-1.05108023005522</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>0.239744067192078</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>26.6335826101613</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>13608310628.7708</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>1.21372264875373</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>92.1562900262242</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>11.066</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:23">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2678,27 +2786,30 @@
         <v>1793187316.05313</v>
       </c>
       <c r="G36">
+        <v>257144811301.673</v>
+      </c>
+      <c r="H36">
         <v>2.27173622615105</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>24752.1068401681</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>47.3371852993157</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>2.74149045788606</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <v>15221540695.0005</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <v>1.31304612393883</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>89.3165894500404</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>10.133</v>
       </c>
     </row>

--- a/GRC_WB_timeseries.xlsx
+++ b/GRC_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC5D1C0-AB55-4742-AA50-A11868AB4BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,33 +472,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>0.63143497705459595</v>
+        <v>0.6314349770545959</v>
       </c>
       <c r="C2">
-        <v>-7.8064795438692602</v>
+        <v>-7.80647954386926</v>
       </c>
       <c r="D2">
-        <v>24.011257952533299</v>
+        <v>24.0112579525333</v>
       </c>
       <c r="E2">
-        <v>4.1378269940584902</v>
+        <v>4.13782699405849</v>
       </c>
       <c r="F2">
-        <v>11638.201069721499</v>
+        <v>11638.2010697215</v>
       </c>
       <c r="G2">
-        <v>44.447326323302498</v>
+        <v>44.4473263233025</v>
       </c>
       <c r="H2">
-        <v>42.501837766950501</v>
+        <v>42.5018377669505</v>
       </c>
       <c r="I2">
-        <v>35.101399796275302</v>
+        <v>35.1013997962753</v>
       </c>
       <c r="J2">
         <v>3.1511816249383</v>
@@ -530,34 +507,33 @@
         <v>15.8840052875083</v>
       </c>
       <c r="L2">
-        <v>-4.2009039419909202</v>
+        <v>-4.20090394199092</v>
       </c>
       <c r="M2">
-        <v>0.80835640430450395</v>
+        <v>0.808356404304504</v>
       </c>
       <c r="N2">
-        <v>23.309875911687001</v>
+        <v>23.309875911687</v>
       </c>
       <c r="O2">
-        <v>59.112657748808601</v>
+        <v>59.1126577488086</v>
       </c>
       <c r="P2">
         <v>108.9</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
-        <v>-7.1208377005018102</v>
+        <v>-7.12083770050181</v>
       </c>
       <c r="D3">
         <v>23.1597595757815</v>
       </c>
       <c r="E3">
-        <v>4.6504145944216297</v>
+        <v>4.65041459442163</v>
       </c>
       <c r="F3">
         <v>12156.9572824221</v>
@@ -566,10 +542,10 @@
         <v>43.8026037175959</v>
       </c>
       <c r="H3">
-        <v>40.435781308036802</v>
+        <v>40.4357813080368</v>
       </c>
       <c r="I3">
-        <v>33.697874379325199</v>
+        <v>33.6978743793252</v>
       </c>
       <c r="J3">
         <v>3.37396832213867</v>
@@ -578,170 +554,169 @@
         <v>14.8415967297389</v>
       </c>
       <c r="L3">
-        <v>-5.8010540026106003</v>
-      </c>
-      <c r="M3" s="2"/>
+        <v>-5.8010540026106</v>
+      </c>
       <c r="N3">
-        <v>21.613046515513801</v>
+        <v>21.6130465155138</v>
       </c>
       <c r="O3">
-        <v>56.857633955106699</v>
+        <v>56.8576339551067</v>
       </c>
       <c r="P3">
         <v>110.5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>0.40318062901496898</v>
+        <v>0.403180629014969</v>
       </c>
       <c r="C4">
-        <v>-6.3862572896569603</v>
+        <v>-6.38625728965696</v>
       </c>
       <c r="D4">
-        <v>20.383102422622599</v>
+        <v>20.3831024226226</v>
       </c>
       <c r="E4">
-        <v>4.6831372706301702</v>
+        <v>4.68313727063017</v>
       </c>
       <c r="F4">
         <v>13782.195640943</v>
       </c>
       <c r="G4">
-        <v>43.202658580219797</v>
+        <v>43.2026585802198</v>
       </c>
       <c r="H4">
-        <v>39.545693554587501</v>
+        <v>39.5456935545875</v>
       </c>
       <c r="I4">
         <v>29.6702347678407</v>
       </c>
       <c r="J4">
-        <v>3.6293587187887302</v>
+        <v>3.62935871878873</v>
       </c>
       <c r="K4">
         <v>13.5804806991988</v>
       </c>
       <c r="L4">
-        <v>-6.1780116428553198</v>
+        <v>-6.17801164285532</v>
       </c>
       <c r="M4">
         <v>0.872591853141785</v>
       </c>
       <c r="N4">
-        <v>21.876970432981501</v>
+        <v>21.8769704329815</v>
       </c>
       <c r="O4">
-        <v>50.053337190463303</v>
+        <v>50.0533371904633</v>
       </c>
       <c r="P4">
         <v>107.9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>0.36332407593727101</v>
+        <v>0.363324075937271</v>
       </c>
       <c r="C5">
-        <v>-6.5062606053612404</v>
+        <v>-6.50626060536124</v>
       </c>
       <c r="D5">
-        <v>18.873492384308499</v>
+        <v>18.8734923843085</v>
       </c>
       <c r="E5">
-        <v>5.7968227429436903</v>
+        <v>5.79682274294369</v>
       </c>
       <c r="F5">
-        <v>18020.612039764001</v>
+        <v>18020.612039764</v>
       </c>
       <c r="G5">
-        <v>43.183069176502499</v>
+        <v>43.1830691765025</v>
       </c>
       <c r="H5">
-        <v>38.467854826011497</v>
+        <v>38.4678548260115</v>
       </c>
       <c r="I5">
-        <v>29.020819770773699</v>
+        <v>29.0208197707737</v>
       </c>
       <c r="J5">
         <v>3.53065027765552</v>
       </c>
       <c r="K5">
-        <v>12.021814312317099</v>
+        <v>12.0218143123171</v>
       </c>
       <c r="L5">
-        <v>-8.1001282459036705</v>
+        <v>-8.100128245903671</v>
       </c>
       <c r="M5">
-        <v>0.47763636708259599</v>
+        <v>0.477636367082596</v>
       </c>
       <c r="N5">
         <v>20.2520438018772</v>
       </c>
       <c r="O5">
-        <v>47.894312155082197</v>
+        <v>47.8943121550822</v>
       </c>
       <c r="P5">
         <v>104.3</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>0.45019042491912797</v>
+        <v>0.450190424919128</v>
       </c>
       <c r="C6">
-        <v>-5.7420140026706896</v>
+        <v>-5.74201400267069</v>
       </c>
       <c r="D6">
-        <v>20.609310913622299</v>
+        <v>20.6093109136223</v>
       </c>
       <c r="E6">
-        <v>5.3778663459585099</v>
+        <v>5.37786634595851</v>
       </c>
       <c r="F6">
-        <v>21449.255276424501</v>
+        <v>21449.2552764245</v>
       </c>
       <c r="G6">
-        <v>44.559387459953498</v>
+        <v>44.5593874599535</v>
       </c>
       <c r="H6">
-        <v>36.787764444811501</v>
+        <v>36.7877644448115</v>
       </c>
       <c r="I6">
-        <v>29.216006758945799</v>
+        <v>29.2160067589458</v>
       </c>
       <c r="J6">
-        <v>2.8988481075817099</v>
+        <v>2.89884810758171</v>
       </c>
       <c r="K6">
-        <v>11.258687258687299</v>
+        <v>11.2586872586873</v>
       </c>
       <c r="L6">
-        <v>-8.9150536883050293</v>
+        <v>-8.915053688305029</v>
       </c>
       <c r="M6">
-        <v>0.48933625221252403</v>
+        <v>0.489336252212524</v>
       </c>
       <c r="N6">
         <v>19.6220114639512</v>
       </c>
       <c r="O6">
-        <v>49.825317672567998</v>
+        <v>49.825317672568</v>
       </c>
       <c r="P6">
         <v>105.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -749,40 +724,40 @@
         <v>0.351383656263351</v>
       </c>
       <c r="C7">
-        <v>-7.5186033522030398</v>
+        <v>-7.51860335220304</v>
       </c>
       <c r="D7">
-        <v>20.992530288314899</v>
+        <v>20.9925302883149</v>
       </c>
       <c r="E7">
-        <v>1.1835063549328899</v>
+        <v>1.18350635493289</v>
       </c>
       <c r="F7">
         <v>22054.1315756886</v>
       </c>
       <c r="G7">
-        <v>43.928487332670997</v>
+        <v>43.928487332671</v>
       </c>
       <c r="H7">
-        <v>37.074367980499296</v>
+        <v>37.0743679804993</v>
       </c>
       <c r="I7">
-        <v>29.363003150825801</v>
+        <v>29.3630031508258</v>
       </c>
       <c r="J7">
-        <v>3.5450727333507701</v>
+        <v>3.54507273335077</v>
       </c>
       <c r="K7">
-        <v>11.235259054943301</v>
+        <v>11.2352590549433</v>
       </c>
       <c r="L7">
-        <v>-6.3658596140506498</v>
+        <v>-6.36585961405065</v>
       </c>
       <c r="M7">
-        <v>0.50652414560318004</v>
+        <v>0.50652414560318</v>
       </c>
       <c r="N7">
-        <v>20.792882370307101</v>
+        <v>20.7928823703071</v>
       </c>
       <c r="O7">
         <v>50.3555334391407</v>
@@ -791,68 +766,68 @@
         <v>109.9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>0.35753244161605802</v>
+        <v>0.357532441616058</v>
       </c>
       <c r="C8">
         <v>-10.9919390863757</v>
       </c>
       <c r="D8">
-        <v>20.774972803753599</v>
+        <v>20.7749728037536</v>
       </c>
       <c r="E8">
-        <v>6.4433976248743603</v>
+        <v>6.44339762487436</v>
       </c>
       <c r="F8">
-        <v>24416.023297027499</v>
+        <v>24416.0232970275</v>
       </c>
       <c r="G8">
-        <v>43.124818084089299</v>
+        <v>43.1248180840893</v>
       </c>
       <c r="H8">
-        <v>36.077184259600102</v>
+        <v>36.0771842596001</v>
       </c>
       <c r="I8">
-        <v>30.329773779726999</v>
+        <v>30.329773779727</v>
       </c>
       <c r="J8">
-        <v>3.1959468414454499</v>
+        <v>3.19594684144545</v>
       </c>
       <c r="K8">
-        <v>10.751385041551201</v>
+        <v>10.7513850415512</v>
       </c>
       <c r="L8">
-        <v>-6.0126307242630199</v>
+        <v>-6.01263072426302</v>
       </c>
       <c r="M8">
-        <v>0.63043278455734297</v>
+        <v>0.630432784557343</v>
       </c>
       <c r="N8">
-        <v>20.311352544431202</v>
+        <v>20.3113525444312</v>
       </c>
       <c r="O8">
-        <v>51.104746583480697</v>
+        <v>51.1047465834807</v>
       </c>
       <c r="P8">
         <v>105.3</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>0.26193070411682101</v>
+        <v>0.261930704116821</v>
       </c>
       <c r="C9">
-        <v>-14.186957094595799</v>
+        <v>-14.1869570945958</v>
       </c>
       <c r="D9">
-        <v>21.748187468445899</v>
+        <v>21.7481874684459</v>
       </c>
       <c r="E9">
         <v>3.50686976639459</v>
@@ -861,37 +836,37 @@
         <v>28440.7625328955</v>
       </c>
       <c r="G9">
-        <v>44.705060629349397</v>
+        <v>44.7050606293494</v>
       </c>
       <c r="H9">
-        <v>37.235244984635102</v>
+        <v>37.2352449846351</v>
       </c>
       <c r="I9">
-        <v>32.777494350458497</v>
+        <v>32.7774943504585</v>
       </c>
       <c r="J9">
-        <v>2.8950032151657799</v>
+        <v>2.89500321516578</v>
       </c>
       <c r="K9">
         <v>10.5442873728061</v>
       </c>
       <c r="L9">
-        <v>-6.7951029219740704</v>
+        <v>-6.79510292197407</v>
       </c>
       <c r="M9">
-        <v>0.52350783348083496</v>
+        <v>0.523507833480835</v>
       </c>
       <c r="N9">
-        <v>20.544064700684601</v>
+        <v>20.5440647006846</v>
       </c>
       <c r="O9">
-        <v>54.525681818904403</v>
+        <v>54.5256818189044</v>
       </c>
       <c r="P9">
         <v>104.6</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -902,25 +877,25 @@
         <v>-14.6094922064777</v>
       </c>
       <c r="D10">
-        <v>22.784791998361499</v>
+        <v>22.7847919983615</v>
       </c>
       <c r="E10">
-        <v>5.7474023820077498E-2</v>
+        <v>0.0574740238200775</v>
       </c>
       <c r="F10">
-        <v>31695.833109220901</v>
+        <v>31695.8331092209</v>
       </c>
       <c r="G10">
-        <v>47.854653547132301</v>
+        <v>47.8546535471323</v>
       </c>
       <c r="H10">
-        <v>37.554128492622397</v>
+        <v>37.5541284926224</v>
       </c>
       <c r="I10">
-        <v>34.320491628131101</v>
+        <v>34.3204916281311</v>
       </c>
       <c r="J10">
-        <v>4.1527970811029302</v>
+        <v>4.15279708110293</v>
       </c>
       <c r="K10">
         <v>10.5395374892775</v>
@@ -932,7 +907,7 @@
         <v>0.267854154109955</v>
       </c>
       <c r="N10">
-        <v>20.489210810513899</v>
+        <v>20.4892108105139</v>
       </c>
       <c r="O10">
         <v>57.1052836264926</v>
@@ -941,21 +916,21 @@
         <v>110.9</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>6.2898904085159302E-2</v>
+        <v>0.0628989040851593</v>
       </c>
       <c r="C11">
-        <v>-10.998286042860499</v>
+        <v>-10.9982860428605</v>
       </c>
       <c r="D11">
         <v>18.7298820095072</v>
       </c>
       <c r="E11">
-        <v>-4.1192760671501096</v>
+        <v>-4.11927606715011</v>
       </c>
       <c r="F11">
         <v>29425.4573200263</v>
@@ -964,7 +939,7 @@
         <v>51.9680969068081</v>
       </c>
       <c r="H11">
-        <v>36.511201684815703</v>
+        <v>36.5112016848157</v>
       </c>
       <c r="I11">
         <v>27.6480773891011</v>
@@ -976,72 +951,72 @@
         <v>10.1516756588078</v>
       </c>
       <c r="L11">
-        <v>-15.406537298355801</v>
+        <v>-15.4065372983558</v>
       </c>
       <c r="M11">
         <v>-0.208124294877052</v>
       </c>
       <c r="N11">
-        <v>20.046721228025898</v>
+        <v>20.0467212280259</v>
       </c>
       <c r="O11">
-        <v>46.377959398608297</v>
+        <v>46.3779593986083</v>
       </c>
       <c r="P11">
         <v>128.5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>-6.2511667609214797E-2</v>
+        <v>-0.0625116676092148</v>
       </c>
       <c r="C12">
-        <v>-10.209449951121099</v>
+        <v>-10.2094499511211</v>
       </c>
       <c r="D12">
         <v>21.7288329798135</v>
       </c>
       <c r="E12">
-        <v>-5.6937412158002996</v>
+        <v>-5.6937412158003</v>
       </c>
       <c r="F12">
-        <v>26653.048800862602</v>
+        <v>26653.0488008626</v>
       </c>
       <c r="G12">
-        <v>51.078647377557999</v>
+        <v>51.078647377558</v>
       </c>
       <c r="H12">
-        <v>37.953760234547403</v>
+        <v>37.9537602345474</v>
       </c>
       <c r="I12">
         <v>29.1936843254168</v>
       </c>
       <c r="J12">
-        <v>4.7129890776039298</v>
+        <v>4.71298907760393</v>
       </c>
       <c r="K12">
-        <v>12.008020524136001</v>
+        <v>12.008020524136</v>
       </c>
       <c r="L12">
-        <v>-11.124802112562101</v>
+        <v>-11.1248021125621</v>
       </c>
       <c r="M12">
         <v>-0.12720687687397</v>
       </c>
       <c r="N12">
-        <v>20.434679123701901</v>
+        <v>20.4346791237019</v>
       </c>
       <c r="O12">
-        <v>50.922517305230301</v>
+        <v>50.9225173052303</v>
       </c>
       <c r="P12">
-        <v>147.80000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>147.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
@@ -1052,7 +1027,7 @@
         <v>-10.0976272377955</v>
       </c>
       <c r="D13">
-        <v>25.307602793383101</v>
+        <v>25.3076027933831</v>
       </c>
       <c r="E13">
         <v>-9.87677875300243</v>
@@ -1061,60 +1036,60 @@
         <v>25504.7866510124</v>
       </c>
       <c r="G13">
-        <v>54.784128775650203</v>
+        <v>54.7841287756502</v>
       </c>
       <c r="H13">
-        <v>40.739650807893597</v>
+        <v>40.7396508078936</v>
       </c>
       <c r="I13">
         <v>30.9853934922685</v>
       </c>
       <c r="J13">
-        <v>3.3298532335064501</v>
+        <v>3.32985323350645</v>
       </c>
       <c r="K13">
-        <v>13.934440935840399</v>
+        <v>13.9344409358404</v>
       </c>
       <c r="L13">
         <v>-10.7389119947317</v>
       </c>
       <c r="M13">
-        <v>-9.8695188760757405E-2</v>
+        <v>-0.0986951887607574</v>
       </c>
       <c r="N13">
-        <v>22.459271394775701</v>
+        <v>22.4592713947757</v>
       </c>
       <c r="O13">
-        <v>56.292996285651597</v>
+        <v>56.2929962856516</v>
       </c>
       <c r="P13">
         <v>175.1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.19037801027297999</v>
+        <v>-0.19037801027298</v>
       </c>
       <c r="C14">
-        <v>-2.5841850605302401</v>
+        <v>-2.58418506053024</v>
       </c>
       <c r="D14">
-        <v>28.965813961379599</v>
+        <v>28.9658139613796</v>
       </c>
       <c r="E14">
-        <v>-8.3311342109999202</v>
+        <v>-8.33113421099992</v>
       </c>
       <c r="F14">
-        <v>21624.346052551002</v>
+        <v>21624.346052551</v>
       </c>
       <c r="G14">
-        <v>57.376266630225402</v>
+        <v>57.3762666302254</v>
       </c>
       <c r="H14">
-        <v>44.339629198117301</v>
+        <v>44.3396291981173</v>
       </c>
       <c r="I14">
         <v>33.4284650145065</v>
@@ -1123,57 +1098,57 @@
         <v>1.50152696177755</v>
       </c>
       <c r="K14">
-        <v>9.4344752582925508</v>
+        <v>9.434475258292551</v>
       </c>
       <c r="L14">
-        <v>-9.6444758621937705</v>
+        <v>-9.644475862193771</v>
       </c>
       <c r="M14">
-        <v>-0.21724869310855899</v>
+        <v>-0.217248693108559</v>
       </c>
       <c r="N14">
         <v>24.9543887136577</v>
       </c>
       <c r="O14">
-        <v>62.394278975886103</v>
+        <v>62.3942789758861</v>
       </c>
       <c r="P14">
         <v>164.3</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>-7.5443044304847703E-2</v>
+        <v>-0.0754430443048477</v>
       </c>
       <c r="C15">
-        <v>-2.0921622609727399</v>
+        <v>-2.09216226097274</v>
       </c>
       <c r="D15">
-        <v>30.327209111594499</v>
+        <v>30.3272091115945</v>
       </c>
       <c r="E15">
-        <v>-2.2721169988802399</v>
+        <v>-2.27211699888024</v>
       </c>
       <c r="F15">
-        <v>21573.344976280499</v>
+        <v>21573.3449762805</v>
       </c>
       <c r="G15">
-        <v>61.354561233366297</v>
+        <v>61.3545612333663</v>
       </c>
       <c r="H15">
-        <v>43.760762811225199</v>
+        <v>43.7607628112252</v>
       </c>
       <c r="I15">
-        <v>32.627537198852004</v>
+        <v>32.627537198852</v>
       </c>
       <c r="J15">
-        <v>-0.92126945425693096</v>
+        <v>-0.921269454256931</v>
       </c>
       <c r="K15">
-        <v>6.9042193976995101</v>
+        <v>6.90421939769951</v>
       </c>
       <c r="L15">
         <v>-14.0252952861954</v>
@@ -1185,48 +1160,48 @@
         <v>24.7308046940324</v>
       </c>
       <c r="O15">
-        <v>62.954746310446502</v>
+        <v>62.9547463104465</v>
       </c>
       <c r="P15">
         <v>180.5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>-0.13609817624092099</v>
+        <v>-0.136098176240921</v>
       </c>
       <c r="C16">
-        <v>-1.5966340925003299</v>
+        <v>-1.59663409250033</v>
       </c>
       <c r="D16">
-        <v>32.514999005264002</v>
+        <v>32.514999005264</v>
       </c>
       <c r="E16">
-        <v>0.79222506096283496</v>
+        <v>0.792225060962835</v>
       </c>
       <c r="F16">
-        <v>21474.725712389201</v>
+        <v>21474.7257123892</v>
       </c>
       <c r="G16">
         <v>49.7478747922233</v>
       </c>
       <c r="H16">
-        <v>43.194299954024999</v>
+        <v>43.194299954025</v>
       </c>
       <c r="I16">
-        <v>33.918569251302699</v>
+        <v>33.9185692513027</v>
       </c>
       <c r="J16">
         <v>-1.3122609640551</v>
       </c>
       <c r="K16">
-        <v>8.3352360946205106</v>
+        <v>8.335236094620511</v>
       </c>
       <c r="L16">
-        <v>-4.0739052183374902</v>
+        <v>-4.07390521833749</v>
       </c>
       <c r="M16">
         <v>-0.140445962548256</v>
@@ -1235,101 +1210,101 @@
         <v>25.3987231791514</v>
       </c>
       <c r="O16">
-        <v>66.433568256566701</v>
+        <v>66.4335682565667</v>
       </c>
       <c r="P16">
         <v>182.8</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-0.11913940310478199</v>
+        <v>-0.119139403104782</v>
       </c>
       <c r="C17">
-        <v>-0.82819219779972997</v>
+        <v>-0.82819219779973</v>
       </c>
       <c r="D17">
-        <v>32.186377552494299</v>
+        <v>32.1863775524943</v>
       </c>
       <c r="E17">
-        <v>-0.22830189217285099</v>
+        <v>-0.228301892172851</v>
       </c>
       <c r="F17">
-        <v>17980.729823813701</v>
+        <v>17980.7298238137</v>
       </c>
       <c r="G17">
-        <v>52.211164098253398</v>
+        <v>52.2111640982534</v>
       </c>
       <c r="H17">
         <v>43.8507857974366</v>
       </c>
       <c r="I17">
-        <v>33.085423586627002</v>
+        <v>33.085423586627</v>
       </c>
       <c r="J17">
         <v>-1.73588804765284</v>
       </c>
       <c r="K17">
-        <v>7.1451195404056396</v>
+        <v>7.14511954040564</v>
       </c>
       <c r="L17">
-        <v>-6.1854596159171198</v>
+        <v>-6.18545961591712</v>
       </c>
       <c r="M17">
         <v>-0.235559731721878</v>
       </c>
       <c r="N17">
-        <v>25.395910758262101</v>
+        <v>25.3959107582621</v>
       </c>
       <c r="O17">
-        <v>65.271801139121393</v>
+        <v>65.27180113912139</v>
       </c>
       <c r="P17">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>-0.13452722132205999</v>
+        <v>-0.13452722132206</v>
       </c>
       <c r="C18">
         <v>-1.68881636338714</v>
       </c>
       <c r="D18">
-        <v>31.179386016541201</v>
+        <v>31.1793860165412</v>
       </c>
       <c r="E18">
-        <v>-3.1794767841205399E-2</v>
+        <v>-0.0317947678412054</v>
       </c>
       <c r="F18">
         <v>17919.2426377048</v>
       </c>
       <c r="G18">
-        <v>48.855194452152098</v>
+        <v>48.8551944521521</v>
       </c>
       <c r="H18">
-        <v>46.393718570359397</v>
+        <v>46.3937185703594</v>
       </c>
       <c r="I18">
-        <v>32.478276572496299</v>
+        <v>32.4782765724963</v>
       </c>
       <c r="J18">
-        <v>-0.82565397839097299</v>
+        <v>-0.825653978390973</v>
       </c>
       <c r="K18">
-        <v>6.9332488530629997</v>
+        <v>6.933248853063</v>
       </c>
       <c r="L18">
         <v>-0.106048681446585</v>
       </c>
       <c r="M18">
-        <v>-0.12970364093780501</v>
+        <v>-0.129703640937805</v>
       </c>
       <c r="N18">
         <v>27.0349616993722</v>
@@ -1341,7 +1316,7 @@
         <v>183.7</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -1355,66 +1330,66 @@
         <v>34.7793204673102</v>
       </c>
       <c r="E19">
-        <v>1.4731247270235199</v>
+        <v>1.47312472702352</v>
       </c>
       <c r="F19">
-        <v>18631.993012929299</v>
+        <v>18631.9930129293</v>
       </c>
       <c r="G19">
-        <v>47.670388743994998</v>
+        <v>47.670388743995</v>
       </c>
       <c r="H19">
-        <v>45.683676231325002</v>
+        <v>45.683676231325</v>
       </c>
       <c r="I19">
         <v>36.1032862068475</v>
       </c>
       <c r="J19">
-        <v>1.1212545203141999</v>
+        <v>1.1212545203142</v>
       </c>
       <c r="K19">
         <v>6.91722743238289</v>
       </c>
       <c r="L19">
-        <v>0.35855537969867401</v>
+        <v>0.358555379698674</v>
       </c>
       <c r="M19">
-        <v>-8.1244044005870805E-2</v>
+        <v>-0.08124404400587081</v>
       </c>
       <c r="N19">
-        <v>26.742819168846399</v>
+        <v>26.7428191688464</v>
       </c>
       <c r="O19">
-        <v>70.882606674157699</v>
+        <v>70.8826066741577</v>
       </c>
       <c r="P19">
         <v>182.6</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-5.6208048015832901E-2</v>
+        <v>-0.0562080480158329</v>
       </c>
       <c r="C20">
-        <v>-2.9294683717734902</v>
+        <v>-2.92946837177349</v>
       </c>
       <c r="D20">
-        <v>38.630976154137997</v>
+        <v>38.630976154138</v>
       </c>
       <c r="E20">
-        <v>2.0646720789240902</v>
+        <v>2.06467207892409</v>
       </c>
       <c r="F20">
-        <v>19873.401523877099</v>
+        <v>19873.4015238771</v>
       </c>
       <c r="G20">
-        <v>48.021861404971503</v>
+        <v>48.0218614049715</v>
       </c>
       <c r="H20">
-        <v>45.669352162915501</v>
+        <v>45.6693521629155</v>
       </c>
       <c r="I20">
         <v>40.6071874522328</v>
@@ -1423,151 +1398,151 @@
         <v>0.625621413453609</v>
       </c>
       <c r="K20">
-        <v>7.3199976941257896</v>
+        <v>7.31999769412579</v>
       </c>
       <c r="L20">
-        <v>0.53373003279405595</v>
+        <v>0.533730032794056</v>
       </c>
       <c r="M20">
-        <v>0.15397906303405801</v>
+        <v>0.153979063034058</v>
       </c>
       <c r="N20">
-        <v>27.108391976828401</v>
+        <v>27.1083919768284</v>
       </c>
       <c r="O20">
-        <v>79.238163606370904</v>
+        <v>79.2381636063709</v>
       </c>
       <c r="P20">
         <v>189.6</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>1.36982277035713E-2</v>
+        <v>0.0136982277035713</v>
       </c>
       <c r="C21">
-        <v>-1.5012184062926299</v>
+        <v>-1.50121840629263</v>
       </c>
       <c r="D21">
         <v>39.5602917930958</v>
       </c>
       <c r="E21">
-        <v>2.2771806533480801</v>
+        <v>2.27718065334808</v>
       </c>
       <c r="F21">
-        <v>19335.360200296898</v>
+        <v>19335.3602002969</v>
       </c>
       <c r="G21">
-        <v>46.925926044928502</v>
+        <v>46.9259260449285</v>
       </c>
       <c r="H21">
-        <v>44.015263643237198</v>
+        <v>44.0152636432372</v>
       </c>
       <c r="I21">
-        <v>41.029809098077301</v>
+        <v>41.0298090980773</v>
       </c>
       <c r="J21">
-        <v>0.25300752203819099</v>
+        <v>0.253007522038191</v>
       </c>
       <c r="K21">
-        <v>6.6215563073948802</v>
+        <v>6.62155630739488</v>
       </c>
       <c r="L21">
-        <v>0.78841690286998101</v>
+        <v>0.788416902869981</v>
       </c>
       <c r="M21">
         <v>0.162428334355354</v>
       </c>
       <c r="N21">
-        <v>25.932435965494701</v>
+        <v>25.9324359654947</v>
       </c>
       <c r="O21">
-        <v>80.590100891172995</v>
+        <v>80.59010089117299</v>
       </c>
       <c r="P21">
         <v>183.7</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>3.1950838863849598E-2</v>
+        <v>0.0319508388638496</v>
       </c>
       <c r="C22">
-        <v>-6.4866420039279404</v>
+        <v>-6.48664200392794</v>
       </c>
       <c r="D22">
-        <v>31.450429504041001</v>
+        <v>31.450429504041</v>
       </c>
       <c r="E22">
-        <v>-9.1962314972697801</v>
+        <v>-9.19623149726978</v>
       </c>
       <c r="F22">
-        <v>17886.733165236001</v>
+        <v>17886.733165236</v>
       </c>
       <c r="G22">
-        <v>58.069881757687803</v>
+        <v>58.0698817576878</v>
       </c>
       <c r="H22">
-        <v>44.001559082914397</v>
+        <v>44.0015590829144</v>
       </c>
       <c r="I22">
-        <v>38.843356944598597</v>
+        <v>38.8433569445986</v>
       </c>
       <c r="J22">
-        <v>-1.2479835558140799</v>
+        <v>-1.24798355581408</v>
       </c>
       <c r="K22">
         <v>5.34587316270943</v>
       </c>
       <c r="L22">
-        <v>-9.5953481255687993</v>
+        <v>-9.595348125568799</v>
       </c>
       <c r="M22">
-        <v>0.11518152803182601</v>
+        <v>0.115181528031826</v>
       </c>
       <c r="N22">
         <v>24.9917156858479</v>
       </c>
       <c r="O22">
-        <v>70.293786448639494</v>
+        <v>70.29378644863949</v>
       </c>
       <c r="P22">
         <v>209.9</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>0.18301144242286699</v>
+        <v>0.183011442422867</v>
       </c>
       <c r="C23">
-        <v>-6.3479528346909397</v>
+        <v>-6.34795283469094</v>
       </c>
       <c r="D23">
-        <v>40.260411800465398</v>
+        <v>40.2604118004654</v>
       </c>
       <c r="E23">
-        <v>8.6544978600213103</v>
+        <v>8.65449786002131</v>
       </c>
       <c r="F23">
         <v>20654.7001960815</v>
       </c>
       <c r="G23">
-        <v>54.832576218443101</v>
+        <v>54.8325762184431</v>
       </c>
       <c r="H23">
-        <v>43.949712794965798</v>
+        <v>43.9497127949658</v>
       </c>
       <c r="I23">
-        <v>47.752250939640497</v>
+        <v>47.7522509396405</v>
       </c>
       <c r="J23">
         <v>1.22382501019854</v>
@@ -1576,54 +1551,54 @@
         <v>4.89689448358315</v>
       </c>
       <c r="L23">
-        <v>-6.8395115177964501</v>
+        <v>-6.83951151779645</v>
       </c>
       <c r="M23">
         <v>0.10138326883316</v>
       </c>
       <c r="N23">
-        <v>25.577735959693499</v>
+        <v>25.5777359596935</v>
       </c>
       <c r="O23">
-        <v>88.012662740105895</v>
+        <v>88.0126627401059</v>
       </c>
       <c r="P23">
         <v>197.8</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>3.7597861140966402E-2</v>
+        <v>0.0375978611409664</v>
       </c>
       <c r="C24">
         <v>-10.3357101038964</v>
       </c>
       <c r="D24">
-        <v>49.019884781247001</v>
+        <v>49.019884781247</v>
       </c>
       <c r="E24">
-        <v>5.7436490252633696</v>
+        <v>5.74364902526337</v>
       </c>
       <c r="F24">
-        <v>20971.834925828301</v>
+        <v>20971.8349258283</v>
       </c>
       <c r="G24">
-        <v>50.594603134885197</v>
+        <v>50.5946031348852</v>
       </c>
       <c r="H24">
-        <v>45.058029502749697</v>
+        <v>45.0580295027497</v>
       </c>
       <c r="I24">
-        <v>58.659323121158202</v>
+        <v>58.6593231211582</v>
       </c>
       <c r="J24">
-        <v>9.6452598128063798</v>
+        <v>9.64525981280638</v>
       </c>
       <c r="K24">
-        <v>5.1691184161729904</v>
+        <v>5.16911841617299</v>
       </c>
       <c r="L24">
         <v>-2.28718031344907</v>
@@ -1632,7 +1607,7 @@
         <v>0.106463775038719</v>
       </c>
       <c r="N24">
-        <v>27.669397178603798</v>
+        <v>27.6693971786038</v>
       </c>
       <c r="O24">
         <v>107.679207902405</v>
@@ -1641,39 +1616,39 @@
         <v>178.4</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>9.7846925258636502E-2</v>
+        <v>0.0978469252586365</v>
       </c>
       <c r="C25">
-        <v>-6.1633041820936496</v>
+        <v>-6.16330418209365</v>
       </c>
       <c r="D25">
         <v>43.7082588320458</v>
       </c>
       <c r="E25">
-        <v>2.3321244494581799</v>
+        <v>2.33212444945818</v>
       </c>
       <c r="F25">
         <v>23400.7278817691</v>
       </c>
       <c r="G25">
-        <v>47.194701280312103</v>
+        <v>47.1947012803121</v>
       </c>
       <c r="H25">
-        <v>43.237275420467498</v>
+        <v>43.2372754204675</v>
       </c>
       <c r="I25">
-        <v>48.448031194178398</v>
+        <v>48.4480311941784</v>
       </c>
       <c r="J25">
         <v>3.46480128513402</v>
       </c>
       <c r="K25">
-        <v>7.2694084549449096</v>
+        <v>7.26940845494491</v>
       </c>
       <c r="L25">
         <v>-1.05108023005522</v>
@@ -1682,51 +1657,45 @@
         <v>0.239744067192078</v>
       </c>
       <c r="N25">
-        <v>26.633582610161302</v>
+        <v>26.6335826101613</v>
       </c>
       <c r="O25">
-        <v>92.156290026224198</v>
+        <v>92.1562900262242</v>
       </c>
       <c r="P25">
         <v>165.2</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>-6.3773197719645296</v>
+        <v>-6.37731977196453</v>
       </c>
       <c r="D26">
-        <v>41.979404150724697</v>
+        <v>41.9794041507247</v>
       </c>
       <c r="E26">
-        <v>2.2717362261510501</v>
+        <v>2.27173622615105</v>
       </c>
       <c r="F26">
         <v>24752.1068401681</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
       <c r="I26">
-        <v>47.337185299315699</v>
+        <v>47.3371852993157</v>
       </c>
       <c r="J26">
-        <v>2.7414904578860599</v>
-      </c>
-      <c r="K26" s="2"/>
+        <v>2.74149045788606</v>
+      </c>
       <c r="L26">
         <v>1.3</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
       <c r="O26">
-        <v>89.316589450040397</v>
+        <v>89.3165894500404</v>
       </c>
       <c r="P26">
-        <v>154.80000000000001</v>
+        <v>154.8</v>
       </c>
     </row>
   </sheetData>
